--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7367,0.0579,0.2144,0.0208</t>
-  </si>
-  <si>
-    <t>0.0162,0.0038,0.0029,0.9909</t>
-  </si>
-  <si>
-    <t>0.7727,0.0468,0.0056,0.1402</t>
-  </si>
-  <si>
-    <t>0.0865,0.0111,0.0039,0.9673</t>
-  </si>
-  <si>
-    <t>0.9945,0.0021,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9899,0.0061,0.0011,0.0010</t>
-  </si>
-  <si>
-    <t>0.9896,0.0059,0.0011,0.0012</t>
-  </si>
-  <si>
-    <t>0.9940,0.0056,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9891,0.0087,0.0013,0.0007</t>
-  </si>
-  <si>
-    <t>0.9777,0.0462,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0011,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9928,0.0059,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.4996,0.1717,0.3736,0.0246</t>
-  </si>
-  <si>
-    <t>0.1744,0.0282,0.8559,0.0021</t>
-  </si>
-  <si>
-    <t>0.6311,0.0440,0.3979,0.0095</t>
-  </si>
-  <si>
-    <t>0.0981,0.0347,0.8871,0.0047</t>
-  </si>
-  <si>
-    <t>0.2449,0.0131,0.8547,0.0126</t>
-  </si>
-  <si>
-    <t>0.0038,0.9904,0.0056,0.0004</t>
-  </si>
-  <si>
-    <t>0.0174,0.9733,0.0110,0.0009</t>
-  </si>
-  <si>
-    <t>0.5654,0.6280,0.0048,0.0007</t>
-  </si>
-  <si>
-    <t>0.0126,0.9741,0.0098,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.9944,0.0037,0.0003</t>
-  </si>
-  <si>
-    <t>0.3986,0.0158,0.3698,0.2263</t>
-  </si>
-  <si>
-    <t>0.1366,0.2544,0.6440,0.0531</t>
-  </si>
-  <si>
-    <t>0.0276,0.0370,0.9574,0.0017</t>
-  </si>
-  <si>
-    <t>0.4937,0.0216,0.6103,0.0075</t>
-  </si>
-  <si>
-    <t>0.1412,0.0188,0.8970,0.0047</t>
-  </si>
-  <si>
-    <t>0.0221,0.0075,0.9620,0.0185</t>
-  </si>
-  <si>
-    <t>0.0007,0.0128,0.9953,0.0007</t>
-  </si>
-  <si>
-    <t>0.0983,0.9252,0.0020,0.0012</t>
-  </si>
-  <si>
-    <t>0.5197,0.1988,0.2776,0.0023</t>
-  </si>
-  <si>
-    <t>0.0012,0.0218,0.9915,0.0048</t>
-  </si>
-  <si>
-    <t>0.0079,0.9541,0.1627,0.0001</t>
-  </si>
-  <si>
-    <t>0.8776,0.1085,0.0141,0.0110</t>
-  </si>
-  <si>
-    <t>0.3492,0.3756,0.2343,0.0038</t>
-  </si>
-  <si>
-    <t>0.7656,0.2340,0.0515,0.0023</t>
-  </si>
-  <si>
-    <t>0.0331,0.9091,0.3880,0.0015</t>
-  </si>
-  <si>
-    <t>0.0122,0.3536,0.8980,0.0050</t>
-  </si>
-  <si>
-    <t>0.0275,0.0248,0.9423,0.0162</t>
-  </si>
-  <si>
-    <t>0.0127,0.1458,0.9010,0.0159</t>
-  </si>
-  <si>
-    <t>0.0616,0.0197,0.9182,0.0096</t>
-  </si>
-  <si>
-    <t>0.0278,0.1757,0.8896,0.0021</t>
-  </si>
-  <si>
-    <t>0.0174,0.9329,0.1624,0.0019</t>
-  </si>
-  <si>
-    <t>0.0072,0.0652,0.9665,0.0020</t>
-  </si>
-  <si>
-    <t>0.0436,0.7405,0.0019,0.4325</t>
-  </si>
-  <si>
-    <t>0.0001,0.9970,0.0021,0.0157</t>
-  </si>
-  <si>
-    <t>0.0003,0.9948,0.0391,0.0024</t>
-  </si>
-  <si>
-    <t>0.0001,0.9987,0.0369,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0362,0.9948,0.0007</t>
-  </si>
-  <si>
-    <t>0.0007,0.0423,0.9967,0.0002</t>
-  </si>
-  <si>
-    <t>0.0110,0.0054,0.9737,0.0193</t>
-  </si>
-  <si>
-    <t>0.0357,0.0092,0.9708,0.0024</t>
-  </si>
-  <si>
-    <t>0.0019,0.0252,0.9880,0.0045</t>
-  </si>
-  <si>
-    <t>0.0089,0.0382,0.9612,0.0017</t>
-  </si>
-  <si>
-    <t>0.9100,0.1176,0.0050,0.0040</t>
-  </si>
-  <si>
-    <t>0.9106,0.0632,0.0393,0.0006</t>
-  </si>
-  <si>
-    <t>0.9814,0.0122,0.0020,0.0019</t>
-  </si>
-  <si>
-    <t>0.0018,0.0205,0.9858,0.0214</t>
-  </si>
-  <si>
-    <t>0.9596,0.0232,0.0027,0.0087</t>
-  </si>
-  <si>
-    <t>0.9909,0.0058,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.9502,0.0535,0.0110,0.0020</t>
-  </si>
-  <si>
-    <t>0.0005,0.7825,0.9813,0.0001</t>
-  </si>
-  <si>
-    <t>0.0258,0.4281,0.8983,0.0073</t>
-  </si>
-  <si>
-    <t>0.0101,0.2213,0.9469,0.0017</t>
-  </si>
-  <si>
-    <t>0.0001,0.9040,0.9892,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0125,0.9926,0.0037</t>
-  </si>
-  <si>
-    <t>0.0173,0.9357,0.0776,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.9900,0.0045,0.0003</t>
-  </si>
-  <si>
-    <t>0.8495,0.0216,0.2330,0.0020</t>
-  </si>
-  <si>
-    <t>0.8842,0.0909,0.0287,0.0040</t>
-  </si>
-  <si>
-    <t>0.0091,0.1793,0.9282,0.0180</t>
-  </si>
-  <si>
-    <t>0.0018,0.8552,0.9223,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.8104,0.9542,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.9844,0.2541,0.0007</t>
-  </si>
-  <si>
-    <t>0.0007,0.9851,0.5500,0.0000</t>
-  </si>
-  <si>
-    <t>0.0318,0.0191,0.1841,0.9129</t>
-  </si>
-  <si>
-    <t>0.0133,0.0052,0.0005,0.9939</t>
-  </si>
-  <si>
-    <t>0.0293,0.0088,0.0009,0.9882</t>
-  </si>
-  <si>
-    <t>0.0376,0.0551,0.0046,0.9699</t>
-  </si>
-  <si>
-    <t>0.0315,0.0169,0.0076,0.9808</t>
-  </si>
-  <si>
-    <t>0.0102,0.0079,0.0017,0.9933</t>
-  </si>
-  <si>
-    <t>0.0008,0.9808,0.7774,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.1444,0.9858,0.0006</t>
-  </si>
-  <si>
-    <t>0.0007,0.9037,0.6016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0045,0.5560,0.9466,0.0004</t>
-  </si>
-  <si>
-    <t>0.0017,0.9210,0.7958,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.8739,0.8434,0.0001</t>
-  </si>
-  <si>
-    <t>0.9917,0.0026,0.0025,0.0017</t>
-  </si>
-  <si>
-    <t>0.9741,0.0295,0.0047,0.0005</t>
-  </si>
-  <si>
-    <t>0.9807,0.0375,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9792,0.0170,0.0014,0.0018</t>
-  </si>
-  <si>
-    <t>0.9921,0.0057,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9885,0.0069,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.9867,0.0129,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.9879,0.0075,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9963,0.0020,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9957,0.0029,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0009,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9944,0.0020,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.9900,0.0120,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9817,0.0283,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9956,0.0019,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9947,0.0049,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0015,0.9986,0.0018</t>
-  </si>
-  <si>
-    <t>0.0299,0.0249,0.9538,0.0043</t>
-  </si>
-  <si>
-    <t>0.6251,0.0350,0.1416,0.1284</t>
-  </si>
-  <si>
-    <t>0.0851,0.0118,0.9403,0.0008</t>
-  </si>
-  <si>
-    <t>0.0009,0.9958,0.0032,0.0005</t>
-  </si>
-  <si>
-    <t>0.0217,0.9676,0.0058,0.0015</t>
-  </si>
-  <si>
-    <t>0.0236,0.9693,0.0023,0.0015</t>
-  </si>
-  <si>
-    <t>0.1817,0.8585,0.0161,0.0012</t>
-  </si>
-  <si>
-    <t>0.0197,0.9636,0.0097,0.0020</t>
-  </si>
-  <si>
-    <t>0.0099,0.9830,0.0041,0.0002</t>
-  </si>
-  <si>
-    <t>0.3695,0.7213,0.0072,0.0002</t>
-  </si>
-  <si>
-    <t>0.6704,0.0580,0.2532,0.0291</t>
-  </si>
-  <si>
-    <t>0.1288,0.0175,0.8860,0.0157</t>
-  </si>
-  <si>
-    <t>0.6310,0.0919,0.1972,0.0689</t>
-  </si>
-  <si>
-    <t>0.5283,0.1321,0.4287,0.0193</t>
-  </si>
-  <si>
-    <t>0.2079,0.2779,0.0505,0.5851</t>
-  </si>
-  <si>
-    <t>0.0001,0.9987,0.0057,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.9921,0.0922,0.0011</t>
-  </si>
-  <si>
-    <t>0.0077,0.9761,0.0119,0.0053</t>
-  </si>
-  <si>
-    <t>0.0001,0.9802,0.9027,0.0000</t>
-  </si>
-  <si>
-    <t>0.0275,0.9598,0.1090,0.0003</t>
-  </si>
-  <si>
-    <t>0.4697,0.4931,0.1028,0.0026</t>
-  </si>
-  <si>
-    <t>0.8124,0.3302,0.0065,0.0004</t>
-  </si>
-  <si>
-    <t>0.9862,0.0064,0.0019,0.0016</t>
-  </si>
-  <si>
-    <t>0.9489,0.0024,0.0036,0.0492</t>
-  </si>
-  <si>
-    <t>0.9803,0.0074,0.0020,0.0049</t>
-  </si>
-  <si>
-    <t>0.9730,0.0090,0.0103,0.0025</t>
-  </si>
-  <si>
-    <t>0.9865,0.0090,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.9894,0.0065,0.0026,0.0005</t>
-  </si>
-  <si>
-    <t>0.9871,0.0070,0.0023,0.0010</t>
-  </si>
-  <si>
-    <t>0.9695,0.0151,0.0151,0.0017</t>
-  </si>
-  <si>
-    <t>0.0018,0.8722,0.9152,0.0003</t>
-  </si>
-  <si>
-    <t>0.0070,0.3147,0.9082,0.0004</t>
-  </si>
-  <si>
-    <t>0.0099,0.5069,0.8296,0.0013</t>
-  </si>
-  <si>
-    <t>0.0073,0.0629,0.9727,0.0004</t>
-  </si>
-  <si>
-    <t>0.5653,0.0455,0.4217,0.0322</t>
-  </si>
-  <si>
-    <t>0.7135,0.0186,0.2157,0.0307</t>
-  </si>
-  <si>
-    <t>0.5842,0.0125,0.5898,0.0071</t>
-  </si>
-  <si>
-    <t>0.4192,0.2711,0.2829,0.0959</t>
-  </si>
-  <si>
-    <t>0.0445,0.0023,0.0015,0.9853</t>
-  </si>
-  <si>
-    <t>0.0008,0.0033,0.0009,0.9986</t>
-  </si>
-  <si>
-    <t>0.0115,0.0215,0.0011,0.9911</t>
-  </si>
-  <si>
-    <t>0.0073,0.0031,0.0021,0.9953</t>
-  </si>
-  <si>
-    <t>0.0008,0.8463,0.8145,0.0012</t>
-  </si>
-  <si>
-    <t>0.9547,0.0180,0.0187,0.0038</t>
-  </si>
-  <si>
-    <t>0.2514,0.7418,0.0443,0.0067</t>
-  </si>
-  <si>
-    <t>0.9684,0.0088,0.0002,0.0125</t>
-  </si>
-  <si>
-    <t>0.7189,0.3547,0.0214,0.0019</t>
-  </si>
-  <si>
-    <t>0.9809,0.0058,0.0023,0.0048</t>
-  </si>
-  <si>
-    <t>0.6435,0.0155,0.1810,0.1185</t>
-  </si>
-  <si>
-    <t>0.9800,0.0142,0.0045,0.0016</t>
-  </si>
-  <si>
-    <t>0.0001,0.0459,0.9963,0.0007</t>
-  </si>
-  <si>
-    <t>0.7855,0.0039,0.1556,0.0322</t>
-  </si>
-  <si>
-    <t>0.8318,0.0342,0.2229,0.0041</t>
-  </si>
-  <si>
-    <t>0.5583,0.5279,0.0218,0.0075</t>
-  </si>
-  <si>
-    <t>0.7244,0.2161,0.0654,0.0231</t>
-  </si>
-  <si>
-    <t>0.7994,0.2106,0.0160,0.0079</t>
-  </si>
-  <si>
-    <t>0.5953,0.1635,0.3120,0.0203</t>
-  </si>
-  <si>
-    <t>0.7769,0.2601,0.0239,0.0024</t>
-  </si>
-  <si>
-    <t>0.8874,0.0902,0.0179,0.0030</t>
-  </si>
-  <si>
-    <t>0.9386,0.0260,0.0121,0.0139</t>
-  </si>
-  <si>
-    <t>0.9799,0.0047,0.0009,0.0089</t>
-  </si>
-  <si>
-    <t>0.9917,0.0024,0.0004,0.0029</t>
-  </si>
-  <si>
-    <t>0.9818,0.0025,0.0044,0.0051</t>
-  </si>
-  <si>
-    <t>0.9592,0.0298,0.0128,0.0035</t>
-  </si>
-  <si>
-    <t>0.9862,0.0052,0.0044,0.0011</t>
-  </si>
-  <si>
-    <t>0.9917,0.0024,0.0008,0.0024</t>
-  </si>
-  <si>
-    <t>0.9764,0.0123,0.0017,0.0052</t>
-  </si>
-  <si>
-    <t>0.8544,0.2370,0.0084,0.0025</t>
-  </si>
-  <si>
-    <t>0.3937,0.7410,0.0063,0.0009</t>
-  </si>
-  <si>
-    <t>0.3351,0.7054,0.0348,0.0016</t>
-  </si>
-  <si>
-    <t>0.7796,0.2043,0.0940,0.0032</t>
-  </si>
-  <si>
-    <t>0.9724,0.0285,0.0018,0.0014</t>
-  </si>
-  <si>
-    <t>0.9124,0.0558,0.0612,0.0015</t>
-  </si>
-  <si>
-    <t>0.9767,0.0215,0.0075,0.0003</t>
-  </si>
-  <si>
-    <t>0.8650,0.1702,0.0234,0.0011</t>
-  </si>
-  <si>
-    <t>0.0046,0.0220,0.9904,0.0012</t>
-  </si>
-  <si>
-    <t>0.9265,0.0595,0.0280,0.0011</t>
-  </si>
-  <si>
-    <t>0.0007,0.0122,0.9954,0.0018</t>
-  </si>
-  <si>
-    <t>0.0042,0.3424,0.9803,0.0008</t>
-  </si>
-  <si>
-    <t>0.0590,0.0151,0.9358,0.0098</t>
-  </si>
-  <si>
-    <t>0.0094,0.2542,0.9598,0.0025</t>
-  </si>
-  <si>
-    <t>0.0020,0.0326,0.9897,0.0015</t>
-  </si>
-  <si>
-    <t>0.0065,0.0093,0.9913,0.0002</t>
-  </si>
-  <si>
-    <t>0.0098,0.0140,0.9850,0.0007</t>
-  </si>
-  <si>
-    <t>0.1669,0.0687,0.7953,0.0073</t>
-  </si>
-  <si>
-    <t>0.6299,0.0613,0.3664,0.0111</t>
-  </si>
-  <si>
-    <t>0.5383,0.0950,0.4596,0.0185</t>
-  </si>
-  <si>
-    <t>0.4949,0.0675,0.5375,0.0177</t>
-  </si>
-  <si>
-    <t>0.0696,0.6157,0.4077,0.0027</t>
-  </si>
-  <si>
-    <t>0.1231,0.0873,0.7973,0.0433</t>
-  </si>
-  <si>
-    <t>0.6031,0.0877,0.2843,0.0455</t>
-  </si>
-  <si>
-    <t>0.4740,0.2350,0.3252,0.0159</t>
-  </si>
-  <si>
-    <t>0.8923,0.1965,0.0050,0.0010</t>
-  </si>
-  <si>
-    <t>0.7046,0.4236,0.0170,0.0008</t>
-  </si>
-  <si>
-    <t>0.9649,0.0849,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9749,0.0226,0.0032,0.0013</t>
-  </si>
-  <si>
-    <t>0.9082,0.1609,0.0068,0.0011</t>
-  </si>
-  <si>
-    <t>0.3849,0.3661,0.2006,0.0072</t>
-  </si>
-  <si>
-    <t>0.6363,0.0504,0.2475,0.0540</t>
-  </si>
-  <si>
-    <t>0.5188,0.0760,0.0781,0.2695</t>
-  </si>
-  <si>
-    <t>0.5383,0.0451,0.3504,0.0744</t>
-  </si>
-  <si>
-    <t>0.6629,0.0979,0.2599,0.0162</t>
-  </si>
-  <si>
-    <t>0.0120,0.0392,0.9486,0.0312</t>
-  </si>
-  <si>
-    <t>0.0420,0.0683,0.8966,0.0102</t>
-  </si>
-  <si>
-    <t>0.0100,0.5709,0.8357,0.0014</t>
-  </si>
-  <si>
-    <t>0.0329,0.0178,0.9373,0.0152</t>
-  </si>
-  <si>
-    <t>0.0054,0.7204,0.7986,0.0007</t>
-  </si>
-  <si>
-    <t>0.9799,0.0202,0.0022,0.0012</t>
-  </si>
-  <si>
-    <t>0.9684,0.0287,0.0053,0.0013</t>
-  </si>
-  <si>
-    <t>0.9762,0.0315,0.0023,0.0009</t>
-  </si>
-  <si>
-    <t>0.9925,0.0040,0.0011,0.0008</t>
-  </si>
-  <si>
-    <t>0.9919,0.0104,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9920,0.0055,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.9851,0.0062,0.0045,0.0014</t>
-  </si>
-  <si>
-    <t>0.9933,0.0083,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0424,0.1690,0.8785,0.0007</t>
-  </si>
-  <si>
-    <t>0.5422,0.1223,0.4882,0.0168</t>
-  </si>
-  <si>
-    <t>0.7969,0.0083,0.1755,0.0263</t>
-  </si>
-  <si>
-    <t>0.0028,0.0780,0.9794,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.1243,0.9949,0.0002</t>
-  </si>
-  <si>
-    <t>0.0208,0.1682,0.8868,0.0016</t>
-  </si>
-  <si>
-    <t>0.0031,0.0102,0.9883,0.0025</t>
-  </si>
-  <si>
-    <t>0.0537,0.0797,0.8806,0.0160</t>
-  </si>
-  <si>
-    <t>0.0006,0.0044,0.9961,0.0013</t>
-  </si>
-  <si>
-    <t>0.0027,0.0084,0.9915,0.0016</t>
-  </si>
-  <si>
-    <t>0.1021,0.1001,0.8114,0.0020</t>
-  </si>
-  <si>
-    <t>0.4090,0.0086,0.7404,0.0090</t>
-  </si>
-  <si>
-    <t>0.5504,0.0087,0.5844,0.0167</t>
-  </si>
-  <si>
-    <t>0.7473,0.0349,0.1669,0.0222</t>
-  </si>
-  <si>
-    <t>0.9950,0.0057,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9692,0.0432,0.0053,0.0004</t>
-  </si>
-  <si>
-    <t>0.9910,0.0037,0.0011,0.0012</t>
-  </si>
-  <si>
-    <t>0.9383,0.0387,0.0344,0.0004</t>
-  </si>
-  <si>
-    <t>0.9924,0.0040,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.9489,0.0445,0.0154,0.0016</t>
-  </si>
-  <si>
-    <t>0.9926,0.0039,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9916,0.0038,0.0025,0.0005</t>
-  </si>
-  <si>
-    <t>0.0240,0.1706,0.8625,0.0050</t>
-  </si>
-  <si>
-    <t>0.0054,0.0561,0.9794,0.0006</t>
-  </si>
-  <si>
-    <t>0.0059,0.0164,0.9779,0.0073</t>
-  </si>
-  <si>
-    <t>0.0458,0.0448,0.9010,0.0076</t>
-  </si>
-  <si>
-    <t>0.0111,0.0059,0.9825,0.0019</t>
-  </si>
-  <si>
-    <t>0.1024,0.0804,0.8374,0.0467</t>
-  </si>
-  <si>
-    <t>0.1330,0.0114,0.9213,0.0031</t>
-  </si>
-  <si>
-    <t>0.0760,0.0722,0.7020,0.1355</t>
-  </si>
-  <si>
-    <t>0.5265,0.0054,0.0448,0.4837</t>
-  </si>
-  <si>
-    <t>0.0268,0.4350,0.0072,0.9303</t>
-  </si>
-  <si>
-    <t>0.0813,0.0050,0.0024,0.9697</t>
-  </si>
-  <si>
-    <t>0.0011,0.0003,0.0008,0.9988</t>
-  </si>
-  <si>
-    <t>0.0047,0.0003,0.0006,0.9979</t>
-  </si>
-  <si>
-    <t>0.7749,0.0424,0.0183,0.0824</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.3836,0.1230,0.0297,0.5593</t>
+  </si>
+  <si>
+    <t>0.0057,0.0005,0.0004,0.9977</t>
+  </si>
+  <si>
+    <t>0.5102,0.0241,0.0028,0.5250</t>
+  </si>
+  <si>
+    <t>0.2152,0.0175,0.0062,0.9000</t>
+  </si>
+  <si>
+    <t>0.9910,0.0095,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9912,0.0056,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9755,0.0140,0.0086,0.0013</t>
+  </si>
+  <si>
+    <t>0.9757,0.0170,0.0100,0.0010</t>
+  </si>
+  <si>
+    <t>0.9911,0.0065,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9819,0.0141,0.0031,0.0008</t>
+  </si>
+  <si>
+    <t>0.9841,0.0069,0.0025,0.0022</t>
+  </si>
+  <si>
+    <t>0.9950,0.0020,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.7458,0.0920,0.1132,0.0139</t>
+  </si>
+  <si>
+    <t>0.0986,0.2659,0.6505,0.0021</t>
+  </si>
+  <si>
+    <t>0.2453,0.0331,0.8161,0.0036</t>
+  </si>
+  <si>
+    <t>0.1316,0.0182,0.9072,0.0018</t>
+  </si>
+  <si>
+    <t>0.7487,0.0578,0.2268,0.0052</t>
+  </si>
+  <si>
+    <t>0.0207,0.9702,0.0180,0.0007</t>
+  </si>
+  <si>
+    <t>0.0029,0.9912,0.0047,0.0003</t>
+  </si>
+  <si>
+    <t>0.1109,0.9014,0.0153,0.0004</t>
+  </si>
+  <si>
+    <t>0.0019,0.9957,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9973,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.4049,0.0110,0.2540,0.2904</t>
+  </si>
+  <si>
+    <t>0.1345,0.0823,0.8009,0.0106</t>
+  </si>
+  <si>
+    <t>0.0207,0.0158,0.9569,0.0247</t>
+  </si>
+  <si>
+    <t>0.1387,0.0057,0.9277,0.0047</t>
+  </si>
+  <si>
+    <t>0.2582,0.0598,0.7274,0.0086</t>
+  </si>
+  <si>
+    <t>0.0748,0.0045,0.9469,0.0104</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9948,0.0371</t>
+  </si>
+  <si>
+    <t>0.3145,0.7957,0.0091,0.0010</t>
+  </si>
+  <si>
+    <t>0.5680,0.0616,0.4101,0.0392</t>
+  </si>
+  <si>
+    <t>0.0031,0.0231,0.9892,0.0086</t>
+  </si>
+  <si>
+    <t>0.0132,0.9531,0.0908,0.0002</t>
+  </si>
+  <si>
+    <t>0.7895,0.2101,0.0269,0.0205</t>
+  </si>
+  <si>
+    <t>0.7248,0.1012,0.1731,0.0046</t>
+  </si>
+  <si>
+    <t>0.7456,0.3258,0.0277,0.0007</t>
+  </si>
+  <si>
+    <t>0.0884,0.8331,0.3218,0.0070</t>
+  </si>
+  <si>
+    <t>0.0017,0.1718,0.9554,0.0077</t>
+  </si>
+  <si>
+    <t>0.0034,0.0416,0.9832,0.0038</t>
+  </si>
+  <si>
+    <t>0.0211,0.0379,0.9548,0.0024</t>
+  </si>
+  <si>
+    <t>0.0703,0.0369,0.9033,0.0152</t>
+  </si>
+  <si>
+    <t>0.0085,0.2326,0.9352,0.0009</t>
+  </si>
+  <si>
+    <t>0.0092,0.9480,0.1294,0.0061</t>
+  </si>
+  <si>
+    <t>0.0156,0.0896,0.9447,0.0030</t>
+  </si>
+  <si>
+    <t>0.4971,0.1547,0.0024,0.2376</t>
+  </si>
+  <si>
+    <t>0.0002,0.9937,0.0083,0.0248</t>
+  </si>
+  <si>
+    <t>0.0010,0.9932,0.0474,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9982,0.0139,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.1204,0.9835,0.0034</t>
+  </si>
+  <si>
+    <t>0.0012,0.6503,0.9741,0.0002</t>
+  </si>
+  <si>
+    <t>0.0866,0.0474,0.8687,0.0171</t>
+  </si>
+  <si>
+    <t>0.0157,0.0082,0.9745,0.0024</t>
+  </si>
+  <si>
+    <t>0.0013,0.0551,0.9921,0.0004</t>
+  </si>
+  <si>
+    <t>0.0034,0.0263,0.9856,0.0004</t>
+  </si>
+  <si>
+    <t>0.9875,0.0112,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.9855,0.0119,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.9918,0.0017,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.0062,0.2257,0.9641,0.0009</t>
+  </si>
+  <si>
+    <t>0.9724,0.0177,0.0115,0.0010</t>
+  </si>
+  <si>
+    <t>0.9890,0.0061,0.0024,0.0008</t>
+  </si>
+  <si>
+    <t>0.9373,0.0920,0.0074,0.0013</t>
+  </si>
+  <si>
+    <t>0.0020,0.7234,0.9598,0.0006</t>
+  </si>
+  <si>
+    <t>0.0024,0.6906,0.7025,0.0210</t>
+  </si>
+  <si>
+    <t>0.0051,0.0064,0.9797,0.0131</t>
+  </si>
+  <si>
+    <t>0.0001,0.8558,0.9894,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.0082,0.9950,0.0004</t>
+  </si>
+  <si>
+    <t>0.0366,0.9419,0.0402,0.0018</t>
+  </si>
+  <si>
+    <t>0.0028,0.9907,0.0110,0.0002</t>
+  </si>
+  <si>
+    <t>0.9588,0.0149,0.0085,0.0027</t>
+  </si>
+  <si>
+    <t>0.5770,0.3220,0.1565,0.0051</t>
+  </si>
+  <si>
+    <t>0.0036,0.0313,0.9783,0.0102</t>
+  </si>
+  <si>
+    <t>0.0029,0.8131,0.8647,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.9019,0.9719,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9908,0.2343,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.9856,0.3953,0.0003</t>
+  </si>
+  <si>
+    <t>0.0138,0.0023,0.0227,0.9800</t>
+  </si>
+  <si>
+    <t>0.0104,0.0027,0.0006,0.9954</t>
+  </si>
+  <si>
+    <t>0.0238,0.0021,0.0001,0.9933</t>
+  </si>
+  <si>
+    <t>0.0312,0.0097,0.0025,0.9867</t>
+  </si>
+  <si>
+    <t>0.0582,0.0063,0.0434,0.9517</t>
+  </si>
+  <si>
+    <t>0.0036,0.0320,0.0023,0.9942</t>
+  </si>
+  <si>
+    <t>0.0013,0.9662,0.7589,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.7694,0.9811,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.7327,0.9101,0.0003</t>
+  </si>
+  <si>
+    <t>0.0031,0.7098,0.9241,0.0008</t>
+  </si>
+  <si>
+    <t>0.0010,0.9660,0.6520,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.8091,0.8653,0.0005</t>
+  </si>
+  <si>
+    <t>0.9868,0.0134,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.9847,0.0071,0.0036,0.0020</t>
+  </si>
+  <si>
+    <t>0.9862,0.0225,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9817,0.0087,0.0005,0.0029</t>
+  </si>
+  <si>
+    <t>0.9851,0.0154,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9932,0.0046,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9909,0.0066,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9802,0.0180,0.0033,0.0011</t>
+  </si>
+  <si>
+    <t>0.9913,0.0073,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9913,0.0057,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.9896,0.0040,0.0026,0.0015</t>
+  </si>
+  <si>
+    <t>0.9951,0.0019,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9924,0.0050,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9960,0.0013,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9930,0.0045,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9910,0.0051,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.0031,0.0106,0.9786,0.0253</t>
+  </si>
+  <si>
+    <t>0.2338,0.0335,0.7858,0.0097</t>
+  </si>
+  <si>
+    <t>0.3443,0.1190,0.2993,0.3740</t>
+  </si>
+  <si>
+    <t>0.0707,0.0181,0.9133,0.0136</t>
+  </si>
+  <si>
+    <t>0.0219,0.9639,0.0072,0.0044</t>
+  </si>
+  <si>
+    <t>0.0043,0.9889,0.0030,0.0007</t>
+  </si>
+  <si>
+    <t>0.0215,0.9682,0.0024,0.0034</t>
+  </si>
+  <si>
+    <t>0.0100,0.9845,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.0276,0.9657,0.0069,0.0007</t>
+  </si>
+  <si>
+    <t>0.0337,0.9568,0.0061,0.0008</t>
+  </si>
+  <si>
+    <t>0.3861,0.7537,0.0073,0.0006</t>
+  </si>
+  <si>
+    <t>0.5279,0.2227,0.2507,0.0289</t>
+  </si>
+  <si>
+    <t>0.1250,0.0040,0.9424,0.0070</t>
+  </si>
+  <si>
+    <t>0.3600,0.1480,0.4008,0.1371</t>
+  </si>
+  <si>
+    <t>0.4646,0.2349,0.3128,0.0710</t>
+  </si>
+  <si>
+    <t>0.5420,0.0240,0.1538,0.2534</t>
+  </si>
+  <si>
+    <t>0.0004,0.9976,0.0219,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.9927,0.0070,0.0101</t>
+  </si>
+  <si>
+    <t>0.0455,0.8615,0.1390,0.0839</t>
+  </si>
+  <si>
+    <t>0.0001,0.9860,0.8203,0.0001</t>
+  </si>
+  <si>
+    <t>0.0173,0.9771,0.0623,0.0001</t>
+  </si>
+  <si>
+    <t>0.5695,0.4453,0.0609,0.0027</t>
+  </si>
+  <si>
+    <t>0.7452,0.3012,0.0432,0.0021</t>
+  </si>
+  <si>
+    <t>0.9815,0.0164,0.0020,0.0017</t>
+  </si>
+  <si>
+    <t>0.9899,0.0017,0.0015,0.0028</t>
+  </si>
+  <si>
+    <t>0.9755,0.0081,0.0019,0.0097</t>
+  </si>
+  <si>
+    <t>0.9632,0.0249,0.0072,0.0032</t>
+  </si>
+  <si>
+    <t>0.9956,0.0005,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.9762,0.0106,0.0032,0.0033</t>
+  </si>
+  <si>
+    <t>0.9922,0.0021,0.0003,0.0026</t>
+  </si>
+  <si>
+    <t>0.9764,0.0079,0.0066,0.0031</t>
+  </si>
+  <si>
+    <t>0.0018,0.5768,0.9752,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.5024,0.9675,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.2456,0.9808,0.0004</t>
+  </si>
+  <si>
+    <t>0.0095,0.0122,0.9842,0.0014</t>
+  </si>
+  <si>
+    <t>0.6699,0.0407,0.2441,0.0400</t>
+  </si>
+  <si>
+    <t>0.6573,0.0284,0.2565,0.0543</t>
+  </si>
+  <si>
+    <t>0.1524,0.0076,0.9273,0.0123</t>
+  </si>
+  <si>
+    <t>0.3384,0.4840,0.1500,0.1065</t>
+  </si>
+  <si>
+    <t>0.0501,0.0022,0.0036,0.9793</t>
+  </si>
+  <si>
+    <t>0.0011,0.0018,0.0002,0.9991</t>
+  </si>
+  <si>
+    <t>0.0066,0.0025,0.0039,0.9943</t>
+  </si>
+  <si>
+    <t>0.0046,0.0006,0.0333,0.9855</t>
+  </si>
+  <si>
+    <t>0.0005,0.9630,0.6408,0.0012</t>
+  </si>
+  <si>
+    <t>0.9670,0.0265,0.0033,0.0022</t>
+  </si>
+  <si>
+    <t>0.2616,0.7101,0.0830,0.0069</t>
+  </si>
+  <si>
+    <t>0.9839,0.0081,0.0024,0.0021</t>
+  </si>
+  <si>
+    <t>0.3637,0.7007,0.0300,0.0056</t>
+  </si>
+  <si>
+    <t>0.7728,0.2423,0.0498,0.0056</t>
+  </si>
+  <si>
+    <t>0.6743,0.0403,0.2613,0.0729</t>
+  </si>
+  <si>
+    <t>0.9596,0.0187,0.0162,0.0044</t>
+  </si>
+  <si>
+    <t>0.0000,0.0194,0.9945,0.0049</t>
+  </si>
+  <si>
+    <t>0.8962,0.0036,0.1030,0.0091</t>
+  </si>
+  <si>
+    <t>0.9459,0.0136,0.0153,0.0130</t>
+  </si>
+  <si>
+    <t>0.8081,0.1734,0.0377,0.0066</t>
+  </si>
+  <si>
+    <t>0.8778,0.0716,0.0313,0.0105</t>
+  </si>
+  <si>
+    <t>0.8788,0.1326,0.0163,0.0009</t>
+  </si>
+  <si>
+    <t>0.6046,0.3644,0.0181,0.0288</t>
+  </si>
+  <si>
+    <t>0.6846,0.3405,0.0455,0.0023</t>
+  </si>
+  <si>
+    <t>0.6539,0.3619,0.0498,0.0064</t>
+  </si>
+  <si>
+    <t>0.9891,0.0069,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9833,0.0104,0.0006,0.0029</t>
+  </si>
+  <si>
+    <t>0.9878,0.0083,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9864,0.0022,0.0056,0.0024</t>
+  </si>
+  <si>
+    <t>0.9924,0.0026,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.9785,0.0085,0.0053,0.0027</t>
+  </si>
+  <si>
+    <t>0.9906,0.0028,0.0010,0.0019</t>
+  </si>
+  <si>
+    <t>0.9777,0.0055,0.0006,0.0109</t>
+  </si>
+  <si>
+    <t>0.5188,0.5868,0.0197,0.0029</t>
+  </si>
+  <si>
+    <t>0.7952,0.3173,0.0102,0.0008</t>
+  </si>
+  <si>
+    <t>0.6369,0.5368,0.0079,0.0005</t>
+  </si>
+  <si>
+    <t>0.1139,0.1958,0.8487,0.0025</t>
+  </si>
+  <si>
+    <t>0.9738,0.0161,0.0083,0.0012</t>
+  </si>
+  <si>
+    <t>0.8882,0.1946,0.0033,0.0009</t>
+  </si>
+  <si>
+    <t>0.9399,0.0801,0.0036,0.0019</t>
+  </si>
+  <si>
+    <t>0.9711,0.0106,0.0033,0.0082</t>
+  </si>
+  <si>
+    <t>0.0079,0.0115,0.9913,0.0009</t>
+  </si>
+  <si>
+    <t>0.9598,0.0303,0.0149,0.0009</t>
+  </si>
+  <si>
+    <t>0.0095,0.0256,0.9781,0.0021</t>
+  </si>
+  <si>
+    <t>0.0070,0.1087,0.9722,0.0018</t>
+  </si>
+  <si>
+    <t>0.0077,0.0030,0.9886,0.0031</t>
+  </si>
+  <si>
+    <t>0.0003,0.4228,0.9815,0.0006</t>
+  </si>
+  <si>
+    <t>0.0568,0.0669,0.8999,0.0031</t>
+  </si>
+  <si>
+    <t>0.0075,0.0631,0.9723,0.0006</t>
+  </si>
+  <si>
+    <t>0.0050,0.0205,0.9828,0.0006</t>
+  </si>
+  <si>
+    <t>0.3096,0.0406,0.3892,0.3884</t>
+  </si>
+  <si>
+    <t>0.2610,0.0581,0.7303,0.0084</t>
+  </si>
+  <si>
+    <t>0.1714,0.3267,0.4507,0.1262</t>
+  </si>
+  <si>
+    <t>0.3230,0.3903,0.2484,0.0017</t>
+  </si>
+  <si>
+    <t>0.2721,0.5454,0.1840,0.0076</t>
+  </si>
+  <si>
+    <t>0.1525,0.1131,0.7248,0.0016</t>
+  </si>
+  <si>
+    <t>0.5706,0.0638,0.3652,0.0454</t>
+  </si>
+  <si>
+    <t>0.3111,0.2461,0.4640,0.0769</t>
+  </si>
+  <si>
+    <t>0.6103,0.6393,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.2028,0.8713,0.0042,0.0001</t>
+  </si>
+  <si>
+    <t>0.2021,0.8830,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.9246,0.1225,0.0041,0.0004</t>
+  </si>
+  <si>
+    <t>0.9362,0.0979,0.0048,0.0005</t>
+  </si>
+  <si>
+    <t>0.3560,0.3012,0.3929,0.0339</t>
+  </si>
+  <si>
+    <t>0.5035,0.0110,0.4458,0.0803</t>
+  </si>
+  <si>
+    <t>0.4314,0.1824,0.3205,0.1157</t>
+  </si>
+  <si>
+    <t>0.5464,0.1006,0.3802,0.0041</t>
+  </si>
+  <si>
+    <t>0.6259,0.1114,0.2455,0.0483</t>
+  </si>
+  <si>
+    <t>0.0196,0.0614,0.9148,0.0311</t>
+  </si>
+  <si>
+    <t>0.0211,0.6567,0.7418,0.0071</t>
+  </si>
+  <si>
+    <t>0.0344,0.0804,0.9040,0.0013</t>
+  </si>
+  <si>
+    <t>0.0880,0.1109,0.8412,0.0026</t>
+  </si>
+  <si>
+    <t>0.0109,0.1744,0.9266,0.0031</t>
+  </si>
+  <si>
+    <t>0.9932,0.0039,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9935,0.0032,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9920,0.0065,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9836,0.0210,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9550,0.0345,0.0108,0.0023</t>
+  </si>
+  <si>
+    <t>0.9956,0.0023,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0019,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9837,0.0046,0.0038,0.0042</t>
+  </si>
+  <si>
+    <t>0.0200,0.0216,0.9765,0.0012</t>
+  </si>
+  <si>
+    <t>0.2170,0.4350,0.4444,0.0052</t>
+  </si>
+  <si>
+    <t>0.7726,0.0087,0.1433,0.0513</t>
+  </si>
+  <si>
+    <t>0.0024,0.4761,0.9295,0.0010</t>
+  </si>
+  <si>
+    <t>0.0047,0.1915,0.9606,0.0029</t>
+  </si>
+  <si>
+    <t>0.0231,0.1353,0.8797,0.0166</t>
+  </si>
+  <si>
+    <t>0.0005,0.0011,0.9981,0.0011</t>
+  </si>
+  <si>
+    <t>0.0117,0.0856,0.9566,0.0009</t>
+  </si>
+  <si>
+    <t>0.0021,0.0287,0.9900,0.0013</t>
+  </si>
+  <si>
+    <t>0.0073,0.2114,0.9448,0.0046</t>
+  </si>
+  <si>
+    <t>0.1546,0.4325,0.4438,0.0305</t>
+  </si>
+  <si>
+    <t>0.5537,0.0315,0.4668,0.0500</t>
+  </si>
+  <si>
+    <t>0.4650,0.0405,0.6379,0.0097</t>
+  </si>
+  <si>
+    <t>0.6047,0.0783,0.3216,0.0590</t>
+  </si>
+  <si>
+    <t>0.9923,0.0047,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9885,0.0050,0.0015,0.0021</t>
+  </si>
+  <si>
+    <t>0.9875,0.0091,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9856,0.0284,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9809,0.0098,0.0040,0.0017</t>
+  </si>
+  <si>
+    <t>0.8260,0.2435,0.0171,0.0004</t>
+  </si>
+  <si>
+    <t>0.9727,0.0232,0.0069,0.0010</t>
+  </si>
+  <si>
+    <t>0.9795,0.0179,0.0060,0.0005</t>
+  </si>
+  <si>
+    <t>0.0146,0.0826,0.9514,0.0012</t>
+  </si>
+  <si>
+    <t>0.0015,0.4509,0.9725,0.0007</t>
+  </si>
+  <si>
+    <t>0.0027,0.0680,0.9833,0.0011</t>
+  </si>
+  <si>
+    <t>0.0521,0.1262,0.8329,0.0175</t>
+  </si>
+  <si>
+    <t>0.0059,0.0971,0.9535,0.0042</t>
+  </si>
+  <si>
+    <t>0.4425,0.0171,0.6074,0.0297</t>
+  </si>
+  <si>
+    <t>0.0759,0.0924,0.8629,0.0220</t>
+  </si>
+  <si>
+    <t>0.0568,0.0725,0.8812,0.0203</t>
+  </si>
+  <si>
+    <t>0.2125,0.0066,0.0917,0.7933</t>
+  </si>
+  <si>
+    <t>0.1374,0.0441,0.0299,0.9051</t>
+  </si>
+  <si>
+    <t>0.0097,0.0012,0.0015,0.9954</t>
+  </si>
+  <si>
+    <t>0.0086,0.0003,0.0012,0.9955</t>
+  </si>
+  <si>
+    <t>0.0016,0.0011,0.0005,0.9987</t>
+  </si>
+  <si>
+    <t>0.7264,0.0214,0.0705,0.1322</t>
   </si>
 </sst>
 </file>
@@ -1953,10 +1962,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2158,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2287,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2648,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,10 +2830,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2998,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3110,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3127,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3432,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3866,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4653,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4667,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4860,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4874,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5168,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5182,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
